--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1094</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1483</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1368</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>318</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>432</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3154</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>205</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>19</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2589</v>
+        <v>862</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>862</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3636</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3736</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3643</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3903</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4261</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3231</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>253</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3900</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1804</v>
+        <v>632</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>632</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1278</v>
+        <v>4985</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>232</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4985</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2546</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3032</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>508</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2455</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>549</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>511</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>562</v>
+        <v>574</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>535</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3584</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>580</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3774</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1102</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>112</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>230</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2217</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1325</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>201</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3859</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1337</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1796</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1347</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>530</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1334</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3119</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1329</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>210</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3602</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1271</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>174</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2614</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1213</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1123</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1664</v>
+        <v>807</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1137</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>807</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1614</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1154</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>311</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4101</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1068</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>223</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1788</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1033</v>
+        <v>911</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1934</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>911</v>
+        <v>977</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1251</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>977</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>136</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1922</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1002</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>664</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1064</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>594</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1085</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>262</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2611</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1028</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1513</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>780</v>
+        <v>692</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1690</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>692</v>
+        <v>566</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2918</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>566</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>204</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1661</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>486</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>275</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>156</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1156</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>414</v>
+        <v>722</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>204</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>97</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1685</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>722</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>168</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1727</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1014</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>718</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>178</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>212</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1917</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1044</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>272</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2123</v>
+        <v>4982</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1153</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>76</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>203</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4982</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1113</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2140</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>648</v>
+        <v>772</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>426</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>772</v>
+        <v>781</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>299</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>781</v>
+        <v>854</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3066</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1093</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>854</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3422</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1023</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1316</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2254</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1068</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1336</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2850</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1113</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1164</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>952</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1033</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>87</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1108</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1001</v>
+        <v>872</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>163</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2565</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1111</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>872</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1571</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1064</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>513</v>
+        <v>432</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1811</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1021</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1181</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>360</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>225</v>
+        <v>717</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1078</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>506</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>130</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>717</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1070</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>494</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1561</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1184</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>436</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6442</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1168</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>467</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>203</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2821</v>
+        <v>828</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1189</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>564</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>186</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>828</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>446</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>203</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1163</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>424</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">

--- a/output/glo-it.xlsx
+++ b/output/glo-it.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>164</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1844</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1159</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>452</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
